--- a/apps/frontend/src/__tests__/fixtures/rosterFormats/committee-export-2025-05-15.excerpt.xlsx
+++ b/apps/frontend/src/__tests__/fixtures/rosterFormats/committee-export-2025-05-15.excerpt.xlsx
@@ -466,10 +466,10 @@
         <v>001</v>
       </c>
       <c r="D2" t="str">
-        <v>JASON D KLINGER</v>
+        <v>JARED D KLINGSTROM</v>
       </c>
       <c r="E2" t="str">
-        <v>898 GARSON AVE</v>
+        <v>898 GARLAND AVE</v>
       </c>
       <c r="F2" t="str">
         <v>ROCHESTER</v>
@@ -481,7 +481,7 @@
         <v>14609</v>
       </c>
       <c r="I2" t="str">
-        <v>(585) 748-4871</v>
+        <v>(585) 555-0171</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -490,7 +490,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>KLINGER.JASON@GMAIL.COM</v>
+        <v>JKLINGSTROM@EXAMPLE.COM</v>
       </c>
       <c r="M2" t="str">
         <v>Democratic</v>
@@ -499,7 +499,7 @@
         <v>M</v>
       </c>
       <c r="O2" t="str">
-        <v>100050143</v>
+        <v>900110021</v>
       </c>
       <c r="P2" t="str">
         <v>LD 017</v>
@@ -522,10 +522,10 @@
         <v>001</v>
       </c>
       <c r="D3" t="str">
-        <v>GARY R LEVINE</v>
+        <v>GARRETT R LEVANDER</v>
       </c>
       <c r="E3" t="str">
-        <v>54 QUEENS ST</v>
+        <v>54 QUEENSBURY ST</v>
       </c>
       <c r="F3" t="str">
         <v>ROCHESTER</v>
@@ -537,7 +537,7 @@
         <v>14609</v>
       </c>
       <c r="I3" t="str">
-        <v>482-9824</v>
+        <v>555-0124</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -555,7 +555,7 @@
         <v>M</v>
       </c>
       <c r="O3" t="str">
-        <v>018427956</v>
+        <v>018910022</v>
       </c>
       <c r="P3" t="str">
         <v>LD 017</v>
@@ -578,10 +578,10 @@
         <v>006</v>
       </c>
       <c r="D4" t="str">
-        <v>STEPHEN F ROESSNER</v>
+        <v>STEPHEN F ROESSLER</v>
       </c>
       <c r="E4" t="str">
-        <v>252 NAVARRE RD</v>
+        <v>252 NAVARRO RD</v>
       </c>
       <c r="F4" t="str">
         <v>ROCHESTER</v>
@@ -611,7 +611,7 @@
         <v>M</v>
       </c>
       <c r="O4" t="str">
-        <v>100060785</v>
+        <v>900110023</v>
       </c>
       <c r="P4" t="str">
         <v>LD 026</v>
@@ -634,10 +634,10 @@
         <v>001</v>
       </c>
       <c r="D5" t="str">
-        <v>IRIS A BIERI</v>
+        <v>IRIS A BIERWALD</v>
       </c>
       <c r="E5" t="str">
-        <v>215 ROOSEVELT RD</v>
+        <v>215 ROSEWOOD RD</v>
       </c>
       <c r="F5" t="str">
         <v>ROCHESTER</v>
@@ -649,7 +649,7 @@
         <v>14618</v>
       </c>
       <c r="I5" t="str">
-        <v>(937) 266-1574</v>
+        <v>(937) 555-0174</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -658,7 +658,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>IRISBIERI@GMAIL.COM</v>
+        <v>IBIERWALD@EXAMPLE.COM</v>
       </c>
       <c r="M5" t="str">
         <v>Democratic</v>
@@ -667,7 +667,7 @@
         <v>F</v>
       </c>
       <c r="O5" t="str">
-        <v>100123762</v>
+        <v>900110024</v>
       </c>
       <c r="P5" t="str">
         <v>Brighton</v>
@@ -690,7 +690,7 @@
         <v>005</v>
       </c>
       <c r="D6" t="str">
-        <v>DENTON A BROWN</v>
+        <v>DENTON A BRAMWELL</v>
       </c>
       <c r="E6" t="str">
         <v>18 WHITE BIRCH CIR</v>
@@ -723,7 +723,7 @@
         <v>M</v>
       </c>
       <c r="O6" t="str">
-        <v>000211151</v>
+        <v>000910025</v>
       </c>
       <c r="P6" t="str">
         <v>Chili</v>
@@ -746,10 +746,10 @@
         <v>001</v>
       </c>
       <c r="D7" t="str">
-        <v>MARY ANN  GEONIE</v>
+        <v>MARY ANN  GEOGHAN</v>
       </c>
       <c r="E7" t="str">
-        <v>90 LYNNWOOD DR</v>
+        <v>90 LYNNGROVE DR</v>
       </c>
       <c r="F7" t="str">
         <v>BROCKPORT</v>
@@ -761,7 +761,7 @@
         <v>14420</v>
       </c>
       <c r="I7" t="str">
-        <v>(585) 315-1812</v>
+        <v>(585) 555-0112</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>M_GENIE@YAHOO.COM</v>
+        <v>MGEOGHAN@EXAMPLE.COM</v>
       </c>
       <c r="M7" t="str">
         <v>Democratic</v>
@@ -779,7 +779,7 @@
         <v>F</v>
       </c>
       <c r="O7" t="str">
-        <v>014245302</v>
+        <v>014910026</v>
       </c>
       <c r="P7" t="str">
         <v>Clarkson</v>
@@ -802,7 +802,7 @@
         <v>001</v>
       </c>
       <c r="D8" t="str">
-        <v>BRIAN J GRAVELLE</v>
+        <v>BRIAN J GRAVENOR</v>
       </c>
       <c r="E8" t="str">
         <v>308 E ELM ST</v>
@@ -817,7 +817,7 @@
         <v>14445</v>
       </c>
       <c r="I8" t="str">
-        <v>(216) 777-0880</v>
+        <v>(216) 555-0180</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>BRIAN.GRAVELLE@GMAIL.COM</v>
+        <v>BGRAVENOR@EXAMPLE.COM</v>
       </c>
       <c r="M8" t="str">
         <v>Democratic</v>
@@ -835,7 +835,7 @@
         <v>M</v>
       </c>
       <c r="O8" t="str">
-        <v>100071530</v>
+        <v>900110027</v>
       </c>
       <c r="P8" t="str">
         <v>East Rochester</v>
@@ -858,7 +858,7 @@
         <v>002</v>
       </c>
       <c r="D9" t="str">
-        <v>TIMOTHY P GUILLEMETTE</v>
+        <v>TIMOTHY P GUILLERMO</v>
       </c>
       <c r="E9" t="str">
         <v>13 AVANTI DR</v>
@@ -873,7 +873,7 @@
         <v>14606</v>
       </c>
       <c r="I9" t="str">
-        <v>(585) 666-1430</v>
+        <v>(585) 555-0130</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -882,7 +882,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>TIMOTHYPGUILLEMETTE@GMAIL.COM</v>
+        <v>TGUILLERMO@EXAMPLE.COM</v>
       </c>
       <c r="M9" t="str">
         <v>Democratic</v>
@@ -891,7 +891,7 @@
         <v>M</v>
       </c>
       <c r="O9" t="str">
-        <v>100073671</v>
+        <v>900110028</v>
       </c>
       <c r="P9" t="str">
         <v>Gates</v>
@@ -914,10 +914,10 @@
         <v>001</v>
       </c>
       <c r="D10" t="str">
-        <v>LILA H AMIREH-ODEH</v>
+        <v>LEILA H AMARI-ODEN</v>
       </c>
       <c r="E10" t="str">
-        <v>105 DOHRCREST DR</v>
+        <v>105 DOHRWOOD DR</v>
       </c>
       <c r="F10" t="str">
         <v>ROCHESTER</v>
@@ -929,7 +929,7 @@
         <v>14612</v>
       </c>
       <c r="I10" t="str">
-        <v>458-3055</v>
+        <v>555-0155</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -938,7 +938,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>LAMIREH2005@GMAIL.COM</v>
+        <v>LAMARIODEN@EXAMPLE.COM</v>
       </c>
       <c r="M10" t="str">
         <v>Democratic</v>
@@ -947,7 +947,7 @@
         <v>F</v>
       </c>
       <c r="O10" t="str">
-        <v>000078133</v>
+        <v>000910029</v>
       </c>
       <c r="P10" t="str">
         <v>Greece</v>
@@ -970,7 +970,7 @@
         <v>001</v>
       </c>
       <c r="D11" t="str">
-        <v>NANCY A MARSDEN</v>
+        <v>NADINE A MARSTON</v>
       </c>
       <c r="E11" t="str">
         <v>18 GREENRIDGE CRES</v>
@@ -985,7 +985,7 @@
         <v>14464</v>
       </c>
       <c r="I11" t="str">
-        <v>(585) 964-3855</v>
+        <v>(585) 555-0155</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1003,7 +1003,7 @@
         <v>F</v>
       </c>
       <c r="O11" t="str">
-        <v>016140730</v>
+        <v>016910030</v>
       </c>
       <c r="P11" t="str">
         <v>Hamlin</v>
@@ -1026,7 +1026,7 @@
         <v>001</v>
       </c>
       <c r="D12" t="str">
-        <v>MATTHEW C TELESKY</v>
+        <v>MATTHEW C TELFORD</v>
       </c>
       <c r="E12" t="str">
         <v>56 SPARROW DR</v>
@@ -1059,7 +1059,7 @@
         <v>M</v>
       </c>
       <c r="O12" t="str">
-        <v>100006390</v>
+        <v>900110031</v>
       </c>
       <c r="P12" t="str">
         <v>Henrietta</v>
@@ -1082,7 +1082,7 @@
         <v>001</v>
       </c>
       <c r="D13" t="str">
-        <v>LORRY S KNAAK</v>
+        <v>LORRAINE S KNAPPE</v>
       </c>
       <c r="E13" t="str">
         <v>726 LAURELTON RD</v>
@@ -1115,7 +1115,7 @@
         <v>F</v>
       </c>
       <c r="O13" t="str">
-        <v>014659632</v>
+        <v>014910032</v>
       </c>
       <c r="P13" t="str">
         <v>Irondequoit</v>
@@ -1138,7 +1138,7 @@
         <v>001</v>
       </c>
       <c r="D14" t="str">
-        <v>MORRIS W BICKWEAT</v>
+        <v>MORRIS W BICKFORD</v>
       </c>
       <c r="E14" t="str">
         <v>7 SIBLEYVILLE LN</v>
@@ -1153,7 +1153,7 @@
         <v>14472</v>
       </c>
       <c r="I14" t="str">
-        <v>624-4324</v>
+        <v>555-0124</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1171,7 +1171,7 @@
         <v>M</v>
       </c>
       <c r="O14" t="str">
-        <v>018808731</v>
+        <v>018910033</v>
       </c>
       <c r="P14" t="str">
         <v>Mendon</v>
@@ -1194,10 +1194,10 @@
         <v>001</v>
       </c>
       <c r="D15" t="str">
-        <v>AURORA V BRANNIGAN-FROMM</v>
+        <v>AURORA V BRANNOCK-FROST</v>
       </c>
       <c r="E15" t="str">
-        <v>115 PARKHURST DR</v>
+        <v>115 PARKHILL DR</v>
       </c>
       <c r="F15" t="str">
         <v>SPENCERPORT</v>
@@ -1209,7 +1209,7 @@
         <v>14559</v>
       </c>
       <c r="I15" t="str">
-        <v>261-7226</v>
+        <v>555-0126</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1218,7 +1218,7 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>AURORABRANNIGAN@GMAIL.COM</v>
+        <v>ABRANNOCK@EXAMPLE.COM</v>
       </c>
       <c r="M15" t="str">
         <v>Democratic</v>
@@ -1227,7 +1227,7 @@
         <v>F</v>
       </c>
       <c r="O15" t="str">
-        <v>002600623</v>
+        <v>002910034</v>
       </c>
       <c r="P15" t="str">
         <v>Ogden</v>
@@ -1250,7 +1250,7 @@
         <v>001</v>
       </c>
       <c r="D16" t="str">
-        <v>PAULA C CRAWFORD</v>
+        <v>PAULINE C CRANDALL</v>
       </c>
       <c r="E16" t="str">
         <v>78 WAUTOMA BEACH RD</v>
@@ -1265,7 +1265,7 @@
         <v>14468</v>
       </c>
       <c r="I16" t="str">
-        <v>(585) 392-9357</v>
+        <v>(585) 555-0157</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1274,7 +1274,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>PCRAWFORD21@GMAIL.COM</v>
+        <v>PCRANDALL@EXAMPLE.COM</v>
       </c>
       <c r="M16" t="str">
         <v>Democratic</v>
@@ -1283,7 +1283,7 @@
         <v>F</v>
       </c>
       <c r="O16" t="str">
-        <v>020116924</v>
+        <v>020910035</v>
       </c>
       <c r="P16" t="str">
         <v>Parma</v>
@@ -1306,7 +1306,7 @@
         <v>001</v>
       </c>
       <c r="D17" t="str">
-        <v>KEVIN D BERRY</v>
+        <v>KEVIN D BERRIDGE</v>
       </c>
       <c r="E17" t="str">
         <v>15 SAINT MARGARET WAY</v>
@@ -1321,7 +1321,7 @@
         <v>14625</v>
       </c>
       <c r="I17" t="str">
-        <v>(315) 879-1129</v>
+        <v>(315) 555-0129</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1330,7 +1330,7 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>KDBERRY64@GMAIL.COM</v>
+        <v>KBERRIDGE@EXAMPLE.COM</v>
       </c>
       <c r="M17" t="str">
         <v>Democratic</v>
@@ -1339,7 +1339,7 @@
         <v>M</v>
       </c>
       <c r="O17" t="str">
-        <v>100015377</v>
+        <v>900110036</v>
       </c>
       <c r="P17" t="str">
         <v>Penfield</v>
@@ -1362,7 +1362,7 @@
         <v>003</v>
       </c>
       <c r="D18" t="str">
-        <v>JOANNE Y CORSICA</v>
+        <v>JOANNE Y CORVINO</v>
       </c>
       <c r="E18" t="str">
         <v>8 TREETOP DR</v>
@@ -1377,7 +1377,7 @@
         <v>14450</v>
       </c>
       <c r="I18" t="str">
-        <v>(315) 382-5224</v>
+        <v>(315) 555-0124</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>JOANNE.CORSICA@ESC.EDU</v>
+        <v>JCORVINO@EXAMPLE.COM</v>
       </c>
       <c r="M18" t="str">
         <v>Democratic</v>
@@ -1395,7 +1395,7 @@
         <v>F</v>
       </c>
       <c r="O18" t="str">
-        <v>100166078</v>
+        <v>900110037</v>
       </c>
       <c r="P18" t="str">
         <v>Perinton</v>
@@ -1418,10 +1418,10 @@
         <v>001</v>
       </c>
       <c r="D19" t="str">
-        <v>BERNARD T MCCULLEN</v>
+        <v>BERNARD T MCCULLOUGH</v>
       </c>
       <c r="E19" t="str">
-        <v>53 RAND PL</v>
+        <v>53 RANDALL PL</v>
       </c>
       <c r="F19" t="str">
         <v>PITTSFORD</v>
@@ -1433,7 +1433,7 @@
         <v>14534</v>
       </c>
       <c r="I19" t="str">
-        <v>381-9013</v>
+        <v>555-0113</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1451,7 +1451,7 @@
         <v>M</v>
       </c>
       <c r="O19" t="str">
-        <v>013153047</v>
+        <v>013910038</v>
       </c>
       <c r="P19" t="str">
         <v>Pittsford</v>
@@ -1474,7 +1474,7 @@
         <v>001</v>
       </c>
       <c r="D20" t="str">
-        <v>JOHN M LOSER</v>
+        <v>JOHN M LOSEY</v>
       </c>
       <c r="E20" t="str">
         <v>315 STEARNS RD</v>
@@ -1489,7 +1489,7 @@
         <v>14428</v>
       </c>
       <c r="I20" t="str">
-        <v>538-2951</v>
+        <v>555-0151</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1507,7 +1507,7 @@
         <v>M</v>
       </c>
       <c r="O20" t="str">
-        <v>015763965</v>
+        <v>015910039</v>
       </c>
       <c r="P20" t="str">
         <v>Riga</v>
@@ -1530,7 +1530,7 @@
         <v>001</v>
       </c>
       <c r="D21" t="str">
-        <v>SUSAN I SWANTON</v>
+        <v>SUSANNA I SWANBERG</v>
       </c>
       <c r="E21" t="str">
         <v>14 MEADOWOOD</v>
@@ -1545,7 +1545,7 @@
         <v>14543</v>
       </c>
       <c r="I21" t="str">
-        <v>(585) 226-3734</v>
+        <v>(585) 555-0134</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1554,7 +1554,7 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>SSWANTON1@ROCHESTER.RR.COM</v>
+        <v>SSWANBERG@EXAMPLE.COM</v>
       </c>
       <c r="M21" t="str">
         <v>Democratic</v>
@@ -1563,7 +1563,7 @@
         <v>F</v>
       </c>
       <c r="O21" t="str">
-        <v>002046546</v>
+        <v>002910040</v>
       </c>
       <c r="P21" t="str">
         <v>Rush</v>
